--- a/output/g20-ministers-trade-reference.xlsx
+++ b/output/g20-ministers-trade-reference.xlsx
@@ -698,22 +698,22 @@
       </c>
       <c r="K2" s="6" t="inlineStr">
         <is>
-          <t>Chief of Cabinet Office (Jefatura de Gabinete de Ministros)</t>
+          <t>Jefatura de Gabinete de Ministros (Chief of Cabinet's Office)</t>
         </is>
       </c>
       <c r="L2" s="5" t="inlineStr">
         <is>
-          <t>Pablo Lavigne (acting)</t>
+          <t>Pablo Quirno</t>
         </is>
       </c>
       <c r="M2" s="6" t="inlineStr">
         <is>
-          <t>Secretary of Production Coordination (exercising Industry &amp; Commerce functions)</t>
+          <t>Minister of Foreign Affairs, International Trade and Worship (Canciller)</t>
         </is>
       </c>
       <c r="N2" s="6" t="inlineStr">
         <is>
-          <t>Ministry of Economy</t>
+          <t>Ministerio de Relaciones Exteriores, Comercio Internacional y Culto</t>
         </is>
       </c>
       <c r="O2" s="7" t="inlineStr">
@@ -760,17 +760,17 @@
       </c>
       <c r="I3" s="11" t="inlineStr">
         <is>
-          <t>Anika Wells</t>
+          <t>Andrew Charlton</t>
         </is>
       </c>
       <c r="J3" s="12" t="inlineStr">
         <is>
-          <t>Minister for Communications (also Minister for Sport)</t>
+          <t>Cabinet Secretary; Assistant Minister for Science, Technology and the Digital Economy</t>
         </is>
       </c>
       <c r="K3" s="12" t="inlineStr">
         <is>
-          <t>Portfolio of Infrastructure, Transport, Regional Development, Communications, Sport and the Arts (Department of Infrastructure, Transport, Regional Development, Communications, Sport and the Arts)</t>
+          <t>Department of Industry, Science and Resources (also Department of the Prime Minister and Cabinet as Cabinet Secretary)</t>
         </is>
       </c>
       <c r="L3" s="11" t="inlineStr">
@@ -780,12 +780,12 @@
       </c>
       <c r="M3" s="12" t="inlineStr">
         <is>
-          <t>Minister for Trade and Tourism (also Special Minister of State; Deputy Leader of the Government in the Senate)</t>
+          <t>Minister for Trade and Tourism; Special Minister of State</t>
         </is>
       </c>
       <c r="N3" s="12" t="inlineStr">
         <is>
-          <t>Department of Foreign Affairs and Trade (DFAT); trade promotion agency Austrade</t>
+          <t>Department of Foreign Affairs and Trade</t>
         </is>
       </c>
       <c r="O3" s="13" t="inlineStr">
@@ -1577,7 +1577,7 @@
       </c>
       <c r="N14" s="6" t="inlineStr">
         <is>
-          <t>Ministry of Finance and Economy (Ministerstwo Finansow i Gospodarki)</t>
+          <t>Ministry of Finance and Economy (Ministerstwo Finansów i Gospodarki)</t>
         </is>
       </c>
       <c r="O14" s="13" t="inlineStr">
@@ -1629,27 +1629,27 @@
       </c>
       <c r="J15" s="12" t="inlineStr">
         <is>
-          <t>Minister of Digital Development, Communications and Mass Media of the Russian Federation</t>
+          <t>Minister of Digital Development, Communications and Mass Media</t>
         </is>
       </c>
       <c r="K15" s="12" t="inlineStr">
         <is>
-          <t>Ministry of Digital Development, Communications and Mass Media (Mintsifry)</t>
+          <t>Ministry of Digital Development, Communications and Mass Media of the Russian Federation (Mintsifry)</t>
         </is>
       </c>
       <c r="L15" s="11" t="inlineStr">
         <is>
-          <t>Maxim Reshetnikov</t>
+          <t>Anton Alikhanov</t>
         </is>
       </c>
       <c r="M15" s="12" t="inlineStr">
         <is>
-          <t>Minister of Economic Development of the Russian Federation</t>
+          <t>Minister of Industry and Trade</t>
         </is>
       </c>
       <c r="N15" s="12" t="inlineStr">
         <is>
-          <t>Ministry of Economic Development (Minekonomrazvitiya)</t>
+          <t>Ministry of Industry and Trade of the Russian Federation (Minpromtorg)</t>
         </is>
       </c>
       <c r="O15" s="14" t="inlineStr">

--- a/output/g20-ministers-trade-reference.xlsx
+++ b/output/g20-ministers-trade-reference.xlsx
@@ -867,7 +867,7 @@
       </c>
       <c r="P4" s="6" t="inlineStr">
         <is>
-          <t>Digital/technology portfolio also held by: Luciana Santos (Minister of Science, Technology and Innovation). Trade/commerce portfolio also held by: Lucas Pedreira do Couto Ferraz (Secretary of Foreign Trade (SECEX)). Balance: INDEPENDENTLY CONFIRMED. Brazil's full-year 2025 merchandise (goods) trade balance was a SURPLUS of +US$68.3 billion (customs/merchandise basis), per MDIC/SECEX official data. Multiple 2026-dated Brazilian sources corroborate the US$68.3bn figure, including LegisMap and Times Brasil/CNBC, and SECEX's own 2026 outlook statements reference '2025, when the balance closed at +US$68.3 billion.' The 202</t>
+          <t>Digital/technology portfolio also held by: Luciana Santos (Minister of Science, Technology and Innovation).Balance: INDEPENDENTLY CONFIRMED. Brazil's full-year 2025 merchandise (goods) trade balance was a SURPLUS of +US$68.3 billion (customs/merchandise basis), per MDIC/SECEX official data. Multiple 2026-dated Brazilian sources corroborate the US$68.3bn figure, including LegisMap and Times Brasil/CNBC, and SECEX's own 2026 outlook statements reference '2025, when the balance closed at +US$68.3 billion.' The 202</t>
         </is>
       </c>
     </row>

--- a/output/g20-ministers-trade-reference.xlsx
+++ b/output/g20-ministers-trade-reference.xlsx
@@ -19,7 +19,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="1">
-    <numFmt numFmtId="164" formatCode="$#,##0.0;($#,##0.0)"/>
+    <numFmt numFmtId="164" formatCode="$#,##0.0&quot;B&quot;;&quot;−&quot;$#,##0.0&quot;B&quot;"/>
   </numFmts>
   <fonts count="5">
     <font>
